--- a/config/combat_manual.xlsx
+++ b/config/combat_manual.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>戦闘画面</t>
+          <t>战斗画面</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>#Icity/card/helditem/ss_01.png-935-436#\n\n#L00000010#【画面左下】#L00000000#\n\t一時停止\n\tモード切替\n\t戦闘倍速\n\n#L00000010#【画面右下】#L00000000#\n\t通常攻撃\n\t通常スキル\n\t必殺スキル\n\n#L00000010#【画面上部】#L00000000#\n\tターン数\n\tラウンド数\n</t>
+          <t>#Icity/card/helditem/ss_01.png-935-436#\n\n#L00000010#【画面左下角】#L00000000#\n\t暂时停止\n\t模式转换\n\t战斗倍速\n\n#L00000010#【画面右下角】#L00000000#\n\t通常攻击\n\t通常技能\n\t必杀技能\n\n#L00000010#【画面上部】几回合#L00000000#\n\t\n\t轮数\n</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ラウンドとターン数</t>
+          <t>回合数和回合数</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>#L00000010#【ラウンド】#L00000000#\n戦闘中、敵を倒すと、次のラウンドの敵が現れる。\n※精鋭対戦/クロスの場合、交代が実質的に次のラウンド扱いとなる。\n\n#L00000010#【自身のターン】#L00000000#\n仲間が1回行動すると、行動した仲間のターンが終了する。\n※多くのバフ効果は「自身のターン」数を基準に持続時間が設定されている。\n\n#L00000010#【ターン】#L00000000#\n\n戦闘画面上部に表示されているのがターン数で、通常全ての仲間が行動をした時点で1ターン経過とカウントされる。\nターン数の制限があるコンテンツでは、プレイ方法によって異なるルールが適応される。</t>
+          <t>#L00000010#【回合】#L00000000#\n战斗中，打倒敌人，下回合的敌人就会出现。\n※精锐对战/跨服的场合，交替实质上是下一轮处理。\n\n#L00000010#【自身的回合】#L00000000#\n伙伴行动1次，行动了的伙伴的回合结束。\n※多数增益效果是以“自身回合数”为基准设定持续时间。\n\n#L00000010#【回合】#L00000000#\n\n战斗画面上部表示的是回合数，通常全部的伙伴都行动的时候算经过1回合。\n有回合数限制的内容，根据游戏方法适用不同的规则。</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>勝敗条件</t>
+          <t>胜负条件</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>戦闘の判定条件は以下の項目がある\n1)ターン数が尽きる\n2)味方全員が戦闘不能になる\n3)HPの割合が高い側が勝利\n\n異なる戦闘では、異なる勝敗の条件がある。\n1)ノーマルステージ、ハードステージ、ハード+ステージ、試練の道、アリーナ、友達対戦、時空激戦では条件1か条件2を満たすと敗北と判定される。\n\n2)ダンジョン（金貨、経験値、欠片、ギフト）、ボス、特定イベントダンジョンなどでは、条件1または条件2を満たすと戦闘終了と判定される（勝敗は判定されない）\n\n3)精鋭対戦/クロス、ギルド戦では通常、条件2を満たすと敗北と判定され、条件1を満たした場合は条件3に基づいて勝敗が判定される。\n\n4)精鋭の特殊な勝敗判定：精鋭対戦で最大ターンに到達し、双方ともに全滅していない場合、双方のHPが90%以上ならば与えたダメージが多い方が勝利する。いずれか一方のHP割合が90%未満であれば、最終的にHPの割合が高い方が勝利する。</t>
+          <t>战斗的判定条件有以下项目\n1)回合数用尽\n2)我方全员不能战斗\n3)HP比例高的一方胜利\n\n不同的战斗，有不同的胜败条件。\n1)在普通关卡、困难关卡、硬+关卡、试炼之路、竞技场、好友对战、时空激战中，满足条件1或2将被判定为失败。\n\n2)地下城（金币、经验值、碎片、礼物）、BOSS、特定活动地下城等，满足条件1或条件2后判定战斗结束（不判定胜负）\n\n3)精锐对战/跨服、公会战通常满足条件2时判定失败，满足条件1时根据条件3判定胜负。\n\n4)精锐的特殊胜败判定：精锐对战达到最大回合，双方没有全灭的情况下，双方的HP 90%以上给予的伤害多的一方胜利。如果某一方的生命值比例低于90%，那么生命值比例高的一方获胜。</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>覚醒値</t>
+          <t>觉醒值</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>【通常の覚醒値】\n覚醒値の上限：1000ポイント\n初期覚醒値：400ポイント\n\n戦闘によって初期覚醒値が異なる。\n\n・覚醒値の回復ルール\n\n1）攻撃による覚醒値回復：仲間が通常攻撃やスキルを発動すると自身の覚醒値が回復する。\n\n2）攻撃を受けHP減少による覚醒値回復：HPを1%失うごとに覚醒値が回復する。\n\n3）撃破による覚醒値回復：敵を撃破するたびに、ダメージを与えた仲間に一定の覚醒値が報酬として与えられる。\n\n4）戦闘効果による覚醒値回復：通常の仲間スキル、装備アイテム、潜在能力効果などによる覚醒値回復効果がある。\n\n※覚醒値の回復速度は、攻撃による覚醒値回復、被ダメ・HP減少による覚醒値回復、撃破による覚醒値報酬、戦闘効果による覚醒値回復に影響される。</t>
+          <t>【普通觉醒值】\n觉醒值上限：1000点\n初始觉醒值：400点\n\n不同战斗的初始觉醒值也不同。\n\n·觉醒值的回复规则\n\n1)攻击回复觉醒值：伙伴发动普通攻击或技能时自身觉醒值回复。\n\n2)受到攻击时HP减少导致觉醒值回复：HP每损失1%觉醒值就会回复。\n\n3)击破回复觉醒值：每次击破敌人时，给予其伤害的伙伴将获得一定的觉醒值作为报酬。\n\n4)战斗效果的觉醒值回复：有通常的伙伴技能、装备道具、潜在能力效果等的觉醒值回复效果。\n\n※觉醒值的回复速度会受到攻击的觉醒值回复、被废生命值减少的觉醒值回复、击破的觉醒值报酬、战斗效果的觉醒值回复的影响。</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>仲間スキル</t>
+          <t>伙伴技能</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>#L00000010#【アクティブスキル】#L00000000#\n\n・通常攻撃：条件制限なし\n\n・スキル：クールタイムあり\n\n・必殺スキル：覚醒値が満タン時に発動できる。発動後、覚醒値は0になる。\n\n#L00000010#【パッシブスキル】#L00000000#\n\n全体バフ、パッシブスキル、探査機、装備道具、潜能、特殊シーン効果など\n\n仲間のスキルが制御状態にある場合、特定スキルの使用禁止アイコンが表示される。\n\n仲間の全てのアクティブスキルが使用できない場合、その仲間のターンがスキップされる。\n\n一部仲間に付与されたバフ/デバフ効果は解除バフ/デバフによって解除できない。発動者が死亡した場合、効果は消失する。\n\nPVPダメージ増加、PVPダメージ軽減はアリーナモード、フレンド対戦などのモードでのみ有効。\n\n橙装備道具のターン有効と回数有効には制限があり、1V1（精鋭対戦、一部ステージ）モードでは全対戦を合計し（WAVEが変わっても更新せず）、ステージモードではラウンドが変わると有効ターンまたは有効回数を計算し直す。</t>
+          <t>#L00000010#【主动技能】#L00000000#\n\n·普通攻击：没有条件限制\n\n·技能：有冷却时间\n\n·必杀技能：觉醒值满时才能发动。发动后，觉醒值变为0。\n\n#L00000010#【被动技能】#L00000000#\n\n全体增益、被动技能、探测器、装备道具、潜能、特殊场景效果等\n\n伙伴的技能处于控制状态时，会显示特定技能的禁止使用图标。\n\n伙伴的全部的主动技能不能使用的场合，那个伙伴的回合被跳过。\n\n一部分伙伴被赋予的增益 / 减益效果不能通过解除增益 / 减益来解除。发动者死亡的场合，效果消失。\n\nPVP伤害增加、PVP伤害减轻仅在竞技场模式、好友对战等模式下有效。\n\n橙装备道具的回合有效和次数有效有限制，1v1（精锐对战、部分关卡）模式下全部对战合计（WAVE改变也不更新），关卡模式下回合改变后有效回合或有效回数重新计算数量。</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>特殊効果</t>
+          <t>特殊效果</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>特殊効果：復活、味方復活、不死身、擬態、連鎖、隠密などの特殊効果が存在する。</t>
+          <t>特殊效果：存在复活、友方复活、不死身、拟态、连锁、隐密等特殊效果。</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>制御効果</t>
+          <t>控制效果</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>・制御効果一覧\n\n眩暈、石化、凍結、拘束、沈黙、麻痺、混乱、魅了、挑発、扇動、睡眠、熟睡、悪夢、束縛、粘液、黒洞、断絶、封印、転送など\n\n特殊(解除不可)：断絶、封印、転送\n\n支配効果：黒洞、伝送\n\n位置移動：断絶、吹き飛ばし</t>
+          <t>控制效果一览\n\n眩晕、石化、冻结、拘束、沉默、麻痹、混乱、魅惑、挑衅、煽动、睡眠、熟睡、恶梦、束缚、黏液、黑洞、断绝、封印、转送等\n\n特殊（不可解除）：断绝、封印、转送\n\n支配效果：黑洞，传送\n\n位置移动：断绝，爆炸</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>状態異常</t>
+          <t>状态异常</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>戦闘中のデバフ効果は、デバフ効果と持続型デバフ効果などに分類され、解除できる\n\n属性低下系デバフ効果：暗闇、治療減少、治療禁止、威圧\n\n持続型デバフ効果：火傷、中毒、流血、裂刃など\n\n神属性デバフ：第一属性または第二属性が神系の仲間が付与するデバフ効果</t>
+          <t>战斗中的减益效果分为减益效果和持久性减益效果等，可以解除\n\n属性低下系减益效果：黑暗，治疗减少，禁止治疗，威压\n\n持久性减益效果：烧伤，中毒，流血，裂刃等\n\n神属性减益：第一属性或者第二属性是神系伙伴所赋予的减益效果</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>その他バフ効果</t>
+          <t>其他增益效果</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>制御効果やデバフ効果のほかに、以下のようなバフ効果も存在する：\n\nバフ効果、持続回復効果、シールド系効果、蓄電、水盾、引火、氷牢、厄災など</t>
+          <t>除了控制效果和减益效果外，还存在以下增益效果：\n\n增益效果、持续回复效果、护盾系效果、蓄电、水盾、闪点、冰牢、灾厄等</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1850,14 +1850,14 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>复活</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>復活</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>復活</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Revive</t>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>パッシブ：戦闘不能になると、次の行動ターンに復活し、一定量の体力と覚醒値を引き継ぐ\n\n※パッシブ効果と威勢ハチマキの効果が同時に存在する場合は、威勢ハチマキの効果が優先される</t>
+          <t>被动：不能战斗时，在下一个行动回合复活，继承一定量的体力和觉醒值\n\n※被动效果和威势蜂缠的效果同时存在的场合，威势蜂缠的效果优先</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>味方復活</t>
+          <t>盟友复活</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>祝福：味方が戦闘不能になると、復活卵に変化する。復活卵は6回攻撃を受けると破壊される。破壊されなければ、次のターン終了時に復活する\n\nパッシブ効果と威勢ハチマキの効果が同時に存在する場合は、効果の優先度は気勢のハチマキ、パッシブ、祝福の順に発動される</t>
+          <t>祝福：伙伴不能战斗的话，会变成复活卵。复活蛋受到6次攻击后会被破坏。不被破坏的话，下回合结束时复活的\n\n被动效果和气势蜂缠的效果同时存在的场合，效果的优先度按气势蜂缠、被动、祝福的顺序发动</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>戦闘中の不死身効果は、2種類に分類される\n\n種類1：致死ダメージ無効化タイプ\n種類2：体力1で生き残るタイプ\n\n種類1と種類2が同時に発動条件を満たす場合は、種類1が優先的に発動する。\n※不死身効果は、他の効果よりも優先して発動する。</t>
+          <t>战斗中的不死身效果分为两种\n\n种类1：致死伤害无效化类型\n种类2：体力1存活的类型\n\n种类1和种类2同时满足发动条件时，种类1优先发动。\n※不死身效果比其他效果优先发动。</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>変身</t>
+          <t>变身</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>変身後も、自身のステータスを引き継ぐ。\n変身中は、相手の外見とアクティブスキルを必ずコピーする。\n変身目標の攻撃力が自身より高い場合、パッシブ効果をコピーできない場合がある。</t>
+          <t>变身后也继承自身的状态。\n变身中，必须复制对方的外表和主动技能。\n变身目标的攻击力比自身高时，有不能复制被动效果的情况。</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>連鎖</t>
+          <t>连锁</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>連鎖効果を発動した仲間がダメージを受けると、効果が付与された敵にも同じダメージが与えられる。\n\n連鎖効果を発動した仲間が撃破された場合、効果が付与された敵にも同量のダメージを与えられる。</t>
+          <t>发动连锁效果的伙伴受到伤害时，被赋予效果的敌人也会受到同样的伤害。\n\n发动连锁效果的伙伴被击破的场合，被赋予效果的敌人也能给予等量的伤害。</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>隠密</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>攻撃対象として選択できなくなる。\n※範囲ダメージの影響は受ける。</t>
+          <t>不能选择攻击对象。\n※受到范围伤害的影响。</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>奪取</t>
+          <t>抢</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>目標のステータスを一定量奪い、自身のステータスに変換する。\n\nステータスを奪われた敵は撃破されてもステータスは返還されない。\n\n一方、ステータスを奪った側が撃破された場合、ステータスは返還される。</t>
+          <t>夺取一定数量的目标状态，转换成自己的状态。\n\n被夺取状态的敌人即使被击破也不会返还状态。\n\n另一方面，夺取状态的一方被击破的场合，状态被返还。</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>共生対象は戦闘中に同じポジションでHP、覚醒値、バフ効果を共有する\n\n【HPと覚醒値の共有】：共生対象は共通のHPゲージと覚醒値を持ち、HPが0になると同時に敗北する。共生対象の攻撃で獲得した覚醒値は共通の覚醒値に加算され、一方の対象が必殺スキルを発動すると、その共通の覚醒値を消費する。\n\n【バフ効果の共有】：付与されたバフやデバフ効果は共生対象両方に適用される。共生対象のうち1体が行動すると、ターンが1回消費される。\n\n【防御属性の共有】：物理防御および特殊防御の属性は、出場時に選択した形態に基づいてダメージを計算する。\n\n【攻撃属性】：戦闘中に共生対象が攻撃する際の物理攻撃、特殊攻撃、および速度の属性は、形態を切り替えた後のステータスを基に計算される\n\n【一部の装備の特殊処理】：「食べかけリンゴ」、「ブルーギア」などの装備アイテムによる覚醒値回復やHP回復効果は、自身の行動前後に発動するが、1つのターンでは最初の自身の行動でのみ発動する。</t>
+          <t>共生对象在战斗中在相同位置共享HP、觉醒值、增益效果\n\n【共享HP和觉醒值】：共生对象有共通的HP计量和觉醒值，HP变成0的同时失败。攻击共生对象获得的觉醒值与共通的觉醒值相加，一方对象发动必杀技能时，消耗共通的觉醒值。\n\n【增益效果的共享】：被赋予的增益和减益效果适用于共生对象双方。共生对象中有一只采取行动的话，会消耗一次回合。\n\n【防御属性共享】：物理防御和特殊防御属性根据出场时选择的形态计算伤害。\n\n【攻击属性】：战斗中共生对象进行攻击时的物理攻击、特殊攻击以及速度属性，以形态切换后的状态为基础进行计算\n\n【部分装备的特殊处理】：“吃了一半的苹果”、“蓝色齿轮”等装备道具的觉醒值回复和HP回复效果，会在自己行动前后发动，但在一个回合内只能在自己最初的行动时发动。</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>特殊必殺スキル</t>
+          <t>特殊必杀技能</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>必殺スキル：自身が制御状態になった時、必殺スキルを発動できない。</t>
+          <t>必杀技能：自身变成控制状态时，不能发动必杀技能。</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>行動不能</t>
+          <t>无法行动</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>行動不能:断絶、支配系制御または制御効果の中で凍結、睡眠、眩暈、熟睡、悪夢、影魅（味方に選択可能な対象がいない場合）、石化、拘束、封印を受けた場合。</t>
+          <t>无法行动：在断绝、支配系控制或控制效果中受到冻结、睡眠、眩晕、熟睡、恶梦、影魅（我方没有可选择对象的情况）、石化、拘束、封印的情况。</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>HP共有：リンクされた目標がダメージを受けると、そのダメージの一定割合をリンクされた目標に分散する。\n\nHP共有と他の特殊効果の関係</t>
+          <t>HP共享：链接目标受到伤害时，将该伤害的一定比例分散到链接目标上。\n\nHP共享与其他特殊效果的关系</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>憑依</t>
+          <t>附体</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>憑依：主に憑依効果を指す。\n\n憑依期間、鹿に変身してダメージ無効化状態になり（味方の受けるダメージを分散する時、ダメージも受けない）、攻撃は自動攻撃になり、通常攻撃で1体にダメージを与える（通常攻撃はスキル効果を発動できる）。一部霊魂が攻撃力最高の味方に憑依した場合、憑依霊魂は宿主と共に対応するレベルのスキルを発動できる（宿主が通常攻撃を発動する場合、憑依霊魂も一緒に通常攻撃を発動。以下同じ）。憑依霊魂の攻撃時、攻撃系属性を100継承する</t>
+          <t>附身：主要指附身效果。\n\n附身期间，变身成鹿变成伤害无效化状态（分散我方受到的伤害时，也不会受到伤害），攻击变成自动攻击，给予1只普通攻击伤害（普通攻击可以发动技能效果）。部分灵魂附身到攻击力最高的伙伴身上时，附身灵魂会和宿主一起发动对应等级的技能(宿主发动普通攻击时，附身灵魂也会一起发动普通攻击。以下相同)。附身灵魂攻击时，继承100攻击系属性</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2398,14 +2398,14 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
+          <t>头晕得厉害</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>眩暈</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>眩暈</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Dizziness</t>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_xy.png-75-75#\n\n効果：目標を行動不動にする。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_xy.png-75-75#\n\n效果：让目标行动不动。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_sh.png-75-75#\n\n効果：目標を行動不能にし、目標のダメージ減少を一定量上昇させる。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_sh.png-75-75#\n\n效果：使目标无法行动，并使目标的伤害减少一定量。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>凍結</t>
+          <t>冻结</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_bd.png-75-75#\n\n効果：目標を行動不能にする。凍結中、目標が一定量のダメージ受けると解除される。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。\n\n凍結強度：凍結強度が高いほど、凍結を解除するために必要なダメージ量が増える。</t>
+          <t>图标：#Ibattle/buff_icon/logo_bd.png-75-75#\n\n效果：使目标无法行动。冻结中，目标受到一定数量的伤害会解除。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。\n\n冻结强度：冻结强度越高，解除冻结所需的伤害量越高。</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_cr.png-75-75#\n\n効果：目標を行動不能にする。この状態中に火傷効果が付与されると、拘束は解除される。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_cr.png-75-75#\n\n效果：使目标无法行动。当在此状态下施加烧伤效果时，约束被解除。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>沈黙</t>
+          <t>沉默</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_cm.png-75-75#\n\n効果：目標はスキルや必殺スキルを発動できなくなる。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_cm.png-75-75#\n\n效果：目标不能发动技能和必杀技能。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>麻痺</t>
+          <t>麻痹</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_mb.png-75-75#\n\n効果：目標は必殺スキルを発動できなくなる。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_mb.png-75-75#\n\n效果：目标无法发动必杀技能。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_hl.png-75-75#\n\n効果：目標は敵味方関係なくランダムに通常攻撃を行う。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_hl.png-75-75#\n\n效果：目标不分敌我随机进行普通攻击。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_mh.png-75-75#\n\n効果：目標は通常攻撃で味方を攻撃する。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_mh.png-75-75#\n\n效果：目标使用普通攻击攻击盟友。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>挑発</t>
+          <t>挑衅</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_cf.png-75-75#\n\n効果：目標が強制的に挑発の発動者に通常攻撃を行う。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_cf.png-75-75#\n\n效果：目标强制对挑衅发动者进行普通攻击。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>扇動</t>
+          <t>煽动</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_tx.png-75-75#\n\n効果：目標が強制的に扇動の発動者に攻撃を行う。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_tx.png-75-75#\n\n效果：目标强制攻击煽动者。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_sm.png-75-75#\n\n効果：目標を行動不能にする。スキル攻撃を受けると解除される。\n\n解除：解除可能\n\n命中率：制御率と制御無効率によ左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_sm.png-75-75#\n\n效果：使目标无法行动。受到技能攻击后会解除。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率影响。</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_sm1.png-75-75#\n\n効果：目標を行動不能にする。アクティブスキル攻撃を2回受けると解除される。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_sm1.png-75-75#\n\n效果：使目标无法行动。受到2次主动技能攻击后会解除。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>悪夢</t>
+          <t>噩梦</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_my.png-75-75#\n\n効果：目標を攻撃不能にする。アクティブスキル攻撃を2回受けると解除される。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_my.png-75-75#\n\n效果：使目标无法攻击。受到2次主动技能攻击后会解除。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3009,14 +3009,14 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
+          <t>束缚</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>束縛</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>束縛</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Restraint</t>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_sf.png-75-75#\n\n効果：目標を攻撃不能にする。\n\n解除：解除可能\n\n命中率：制御率と制御無効率によって左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_sf.png-75-75#\n\n效果：使目标无法攻击。\n\n解除：可以解除\n\n命中率：根据控制率和控制无效率左右。</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_ny.png-75-75#\n\n目標は通常攻撃とスキルを発動できない。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>图标：#Ibattle/buff_icon/logo_ny.png-75-75#\n\n目标不能发动普通攻击和技能。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>黒洞</t>
+          <t>黑洞</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>効果：目標を行動にし、スキルの攻撃対象に選ばれないようにする。\n\n解除：解除可能\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>效果：将目标变为行动，避免被选为技能的攻击对象。\n\n解除：可以解除\n\n命中率：受控制率和控制无效率的影响。</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>断絶</t>
+          <t>断绝</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>効果：目標を行動不能にし、攻撃対象にも選ばれない。目標に選択されない\n\n解除：解除不可\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>效果：使目标无法行动，也不会被选为攻击对象。目标不被选择\n\n解除：不可解除\n\n命中率：控制率和控制无效率左右。</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>効果：目標を行動不能にする。\n\n解除：解除不可\n\n命中率：制御率と制御無効率に左右される。</t>
+          <t>效果：使目标无法行动。\n\n解除：解除不可\n\n命中率：受控制率和控制无效率影响。</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>転送</t>
+          <t>传输</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>効果:目標を行動不能にし、攻撃対象に選ばれないが、{0}からは目標として選ばれる。\n\n解除：解除不可</t>
+          <t>效果：使目标不能行动，不被选为攻击对象，但被{0}选为目标。\n\n解除：不可解除</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>火傷</t>
+          <t>烧伤</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_zs.png-75-75#\n\n効果：目標を火傷状態にすると、行動開始時に物理/特殊ダメージを一度与える。（一定の物理攻撃/特殊攻撃の割り増し）\n\n聖火火傷：目標の行動ターン前に物理攻撃力に基づく確定ダメージを与える。\n\n重複：火傷は最大5層まで重複可能\n\n解除：解除可能</t>
+          <t>图标：#Ibattle/buff_icon/logo_zs.png-75-75#\n\n效果：使目标处于烧伤状态时，在行动开始时造成一次物理/特殊伤害。（一定物理攻击/特殊攻击加成）\n\n火炬灼伤：在目标行动回合前造成基于物理攻击力的真实伤害。\n\n重复：烧伤最多可重复5层\n\n解除：可解除</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_zd.png-75-75#\n\n効果：目標を中毒状態にすると、行動開始ターンの前に確定ダメージを一度与える（一定の物理攻撃/特殊攻撃の割り増し）\n\n解除：解除可能</t>
+          <t>图标：#Ibattle/buff_icon/logo_zd.png-75-75#\n\n效果：使目标进入中毒状态后，在行动开始回合前造成一次真实伤害（一定物理攻击/特殊攻击加成）\n\n解除：可以解除</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_lx.png-75-75#\n\n効果：目標を流血状態にすると、行動開始ターンの前に確定ダメージを一度与える（一定の物理攻撃/特殊攻撃の割り増し）\n\n重複：流血は最大5層まで重複可能\n\n解除：解除可能</t>
+          <t>图标：#Ibattle/buff_icon/logo_lx.png-75-75#\n\n效果：使目标进入流血状态后，在行动开始回合前造成一次真实伤害（一定物理攻击/特殊攻击加成）\n\n重复：流血最多可重复5层\n\n解除：可解除</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_sl.png-75-75#\n\n効果：目標を裂刃状態にすると、攻撃時に確定ダメージを与える（一定の物理攻撃/特殊攻撃の割り増し）\n\n重複：裂刃は最大3層まで重複可能\n\n解除：解除可能</t>
+          <t>图标：#Ibattle/buff_icon/logo_sl.png-75-75#\n\n效果：使目标进入裂刃状态，攻击时造成真实伤害（一定物理攻击/特殊攻击加成）\n\n重复：裂刃最多可重复3层\n\n解除：可解除</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>暗闇</t>
+          <t>黑暗</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_zm.png-75-75#\n\n効果：目標は一定の確率で攻撃が失敗する\n\n解除：アクティブスキルの暗闇効果は解除可能</t>
+          <t>图标：#Ibattle/buff_icon/logo_zm.png-75-75#\n\n效果：目标有一定几率攻击失败\n\n解除：主动技能的黑暗效果可以解除</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>治療減少</t>
+          <t>治疗减少</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_jl1.png-75-75#\n\n効果：目標は一定の確率で治療効果が減少する\n\n解除：解除可能</t>
+          <t>图标：#Ibattle/buff_icon/logo_jl1.png-75-75#\n\n效果：目标有一定几率减少治疗效果\n\n解除：可以解除</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>治療禁止</t>
+          <t>禁止治疗</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_jl2.png-75-75#\n\n効果：目標は治療効果を受けることができない。\n\n解除：解除可能</t>
+          <t>图标：#Ibattle/buff_icon/logo_jl2.png-75-75#\n\n效果：目标无法获得治疗效果。\n\n解除：可以解除</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>威圧</t>
+          <t>嗤之以鼻</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_ws.png-75-75#\n\n効果：目標の与ダメージを減少させる。金系の目標を攻撃した場合、追加で与ダメージを減少させる\n\n解除：解除可能</t>
+          <t>图标：#Ibattle/buff_icon/logo_ws.png-75-75#\n\n效果：减少目标造成的伤害。攻击金系目标时，额外减少造成伤害\n\n解除：可以解除</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>幽鬼の炎</t>
+          <t>幽灵的火焰</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>アイコン：#Ibattle/buff_icon/logo_ymgh.png-75-75#\n\n特殊なデバフ効果。目標の行動前、または幽鬼の炎が解除された時、目標のHPと覚醒値を減少させる。\n\n解除：解除可能\n\n重複：重複不可</t>
+          <t>图标：#Ibattle/buff_icon/logo_ymgh.png-75-75#\n\n特殊减益效果。目标行动前或幽鬼火焰被解除时，减少目标的生命值和觉醒值。\n\n解除：可以解除\n\n重复：不可重复</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>戦闘中の属性デバフ効果\n\n戦闘中の属性デバフ効果は、一般的に属性が減少する効果を指す。\n例:物理攻撃力の低下、物理防御力の低下など</t>
+          <t>战斗中的属性减益效果\n\n战斗中的属性减益效果一般是指属性减少的效果。\n例：物理攻击力低下、物理防御力低下等</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>バフ効果</t>
+          <t>增益效应</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>バフ効果\n\n戦闘中のバフ効果は、一般的にステータス増加の効果を指す。\n例:物理攻撃力の上昇、物理防御力の上昇など</t>
+          <t>增益效果\n\n战斗中的增益效果一般是指增加状态的效果。\n例：物理攻击力上升、物理防御力上升等</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>持続回復</t>
+          <t>持续恢复</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>回復効果には、継続治癒と継続的な覚醒値回復を含む</t>
+          <t>恢复效果包括持续治愈和持续觉醒值恢复</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>シールド</t>
+          <t>屏蔽</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>ダメージを受けた際、シールドがダメージを吸収する。シールド値が0になるとシールドは消失。\n\n異なる仲間によるシールドは相互に重複でき、同じ仲間によるシールドは重複不可。（特別な説明がある場合を除く）</t>
+          <t>受到伤害时，护盾会吸收伤害。护盾值变为0时，护盾消失。\n\n不同伙伴的护盾可以相互重复，同一伙伴的护盾不可重复。（除非另有说明）</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>全体シールド</t>
+          <t>全屏蔽</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>全体シールドがある間、味方の被ダメージを吸収する。シールド値が0になると全体シールドが破壊される。\n\n全体シールドが存在する場合、そのシールドを破壊した攻撃の超過ダメージ（シールドを超えた分のダメージ）は、シールドの破壊とともに消失する。\n\n全体シールドは重複不可(古い全体シールドは新しい全体シールドに上書きされる)。</t>
+          <t>全体护盾存在期间，吸收我方受到的伤害。护盾值变为0时全体护盾被破坏。\n\n全体护盾存在的场合，破坏那个护盾的攻击的超出伤害（超过护盾的部分的伤害），随着护盾的破坏一起消失。\n\n全体护盾不可重复（旧全体护盾被新全体护盾覆盖）。</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3957,14 +3957,14 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
+          <t>条件</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>蓄電</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>蓄電</t>
-        </is>
-      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>Storage of electricity</t>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>各層ごとに一定量の雷属性スキルダメージが上昇する。\n\nバフ効果ではないため、解除できない。</t>
+          <t>每层增加一定量的雷属性技能伤害。\n\n因为不是增益效果，所以不能解除。</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>水盾は自身が受ける最終ダメージの一定割合を相殺してくれる。(解除不可)</t>
+          <t>水盾会抵消自身最终伤害的一定比例。（不可解除）</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>攻撃時に火傷効果を付与し、効果は数ターン持続。火傷状態の目標はターン開始前に、発動者から一度物理/特殊ダメージを受ける（一定の物理攻撃力/特殊攻撃力割り増し）\n\n引火によって追加された火傷効果は解除可能。</t>
+          <t>攻击时给予烧伤效果，效果持续数回合。烧伤状态的目标在回合开始前，受到一次由发动者造成的物理/特殊伤害（一定的物理攻击力/特殊攻击力加成）\n\n引燃所追加的烧伤效果可以解除。</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>氷牢</t>
+          <t>冰牢</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>目標はターン後に一定量の物理防御力が減少し、一定の確率で凍結が付与される。\n\n氷牢効果はデバフ効果や制御効果に該当せず、解除できない。※発動後の物防減少はデバフ効果、凍結は制御効果に該当し、解除可能。</t>
+          <t>目标在回合后减少一定数量的物理防御力，有一定概率被冻结。\n\n冰牢效果不属于减益效果和控制效果，不能解除。※发动后的物防减少是减益效果，冻结是控制效果，可以解除。</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>厄災</t>
+          <t>灾厄</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>各ターン開始前に、厄災状態の目標は最大HP減少、物理/特殊防御低下、物理/特殊攻撃低下、次回の被ダメージ上昇の中から1つが付与される。\n\n厄災効果自体はデバフ効果には該当せず、解除できない。</t>
+          <t>各回合开始前，灾厄状态的目标从最大生命值减少、物理/特殊防御降低、物理/特殊攻击降低、下次伤害上升中给予1个。\n\n灾厄效果本身不属于减益效果，不能解除。</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
